--- a/config/excel/enemy.xlsx
+++ b/config/excel/enemy.xlsx
@@ -446,22 +446,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,55 +478,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>art_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>chapter</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>combat_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>base_hp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>base_dmg</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>drop_gold</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>drop_relic</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>drop_reroll_reward</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>phase_group</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>quote_group</t>
         </is>
@@ -549,50 +555,55 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>ref</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>ref</t>
         </is>
@@ -611,55 +622,60 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>美术资源 ID（res://assets/characters/mobs/{art_id}/sprite_frames.tres），空=占位方块</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>中文名</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>所属章节 1-5</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>类型：NORMAL/ELITE/BOSS</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>战斗类型：WARRIOR/GUARDIAN/RANGER/CASTER/PRIEST</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>基础血量（会被章节/深度系数缩放）</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>基础攻击力</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>击杀金币</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>是否掉落遗物 1是0否</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>掉落重投奖励次数</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>阶段组外键，指向 phases sheet 的 phase_group</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
         <is>
           <t>台词组外键，指向 quotes sheet 的 quote_group</t>
         </is>
@@ -678,43 +694,48 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>食尸鬼</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>28</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>7</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>20</v>
       </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>PG0001</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>QG0001</t>
         </is>
@@ -733,43 +754,48 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>剧毒蛛母</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>RANGER</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>18</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>20</v>
       </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
         <is>
           <t>PG0002</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>QG0002</t>
         </is>
@@ -788,43 +814,48 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>腐化树人</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>42</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>4</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>20</v>
       </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="inlineStr">
         <is>
           <t>PG0003</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>QG0003</t>
         </is>
@@ -843,43 +874,48 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>哀嚎女妖</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>16</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>20</v>
       </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>PG0004</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>QG0004</t>
         </is>
@@ -898,43 +934,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>月光狼灵</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>PRIEST</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>20</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>20</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="inlineStr">
         <is>
           <t>PG0005</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>QG0005</t>
         </is>
@@ -951,45 +992,46 @@
           <t>ice_yeti</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>雪原雪人</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>36</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>9</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>20</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="inlineStr">
         <is>
           <t>PG0101</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>QG0101</t>
         </is>
@@ -1006,45 +1048,46 @@
           <t>ice_mage</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>霜寒女巫</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>2</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>18</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>4</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>20</v>
       </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>PG0102</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>QG0102</t>
         </is>
@@ -1061,45 +1104,46 @@
           <t>ice_wolf</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>霜鬃狼</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>2</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>RANGER</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>22</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>5</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>PG0103</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>QG0103</t>
         </is>
@@ -1116,45 +1160,46 @@
           <t>ice_golem</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>寒冰石像</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>44</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>4</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>20</v>
       </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>PG0104</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>QG0104</t>
         </is>
@@ -1171,45 +1216,46 @@
           <t>lava_hound</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>地狱火犬</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>30</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>8</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>20</v>
       </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>PG0201</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>QG0201</t>
         </is>
@@ -1226,45 +1272,46 @@
           <t>lava_imp</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>小恶魔</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>3</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>16</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>4</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>20</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>PG0202</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>QG0202</t>
         </is>
@@ -1281,45 +1328,46 @@
           <t>lava_guardian</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>黑铁卫士</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>3</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>48</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>20</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>PG0203</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>QG0203</t>
         </is>
@@ -1336,45 +1384,46 @@
           <t>lava_shaman</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>火焰萨满</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>3</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>PRIEST</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>22</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>20</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
         <is>
           <t>PG0204</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>QG0204</t>
         </is>
@@ -1391,45 +1440,46 @@
           <t>shadow_assassin</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>暗影刺客</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>4</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>RANGER</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>24</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>12</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>20</v>
       </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>PG0301</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>QG0301</t>
         </is>
@@ -1446,45 +1496,46 @@
           <t>shadow_felguard</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>邪能卫兵</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>4</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>46</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>6</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>20</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="inlineStr">
         <is>
           <t>PG0302</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>QG0302</t>
         </is>
@@ -1501,45 +1552,46 @@
           <t>shadow_warlock</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>邪能术士</t>
         </is>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>4</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>20</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>5</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>20</v>
       </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>PG0303</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>QG0303</t>
         </is>
@@ -1556,45 +1608,46 @@
           <t>shadow_knight</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>堕落死亡骑士</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>4</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>34</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>10</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>20</v>
       </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
         <is>
           <t>PG0304</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>QG0304</t>
         </is>
@@ -1611,45 +1664,46 @@
           <t>eternal_sentinel</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>光铸哨兵</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>5</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>40</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>8</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>20</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>PG0401</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>QG0401</t>
         </is>
@@ -1666,45 +1720,46 @@
           <t>eternal_chrono</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>时光龙人</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>5</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>26</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>7</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>20</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="inlineStr">
         <is>
           <t>PG0402</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>QG0402</t>
         </is>
@@ -1721,45 +1776,46 @@
           <t>eternal_archer</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>星界游侠</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>5</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>RANGER</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>22</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>10</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>20</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="inlineStr">
         <is>
           <t>PG0403</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>QG0403</t>
         </is>
@@ -1776,45 +1832,46 @@
           <t>eternal_priest</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>泰坦祭司</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>5</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>PRIEST</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>24</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>20</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="inlineStr">
         <is>
           <t>PG0404</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>QG0404</t>
         </is>
@@ -1833,43 +1890,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
           <t>亡灵巫师</t>
         </is>
       </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>85</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>50</v>
       </c>
-      <c r="J25" t="n">
-        <v>1</v>
-      </c>
       <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
         <v>2</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>PG9001</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>QG9001</t>
         </is>
@@ -1888,43 +1950,48 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>狼人首领</t>
         </is>
       </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>100</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>11</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>50</v>
       </c>
-      <c r="J26" t="n">
-        <v>1</v>
-      </c>
       <c r="K26" t="n">
+        <v>1</v>
+      </c>
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>PG9002</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>QG9002</t>
         </is>
@@ -1941,45 +2008,46 @@
           <t>elite_frost_wyrm</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>霜龙幼崽</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>2</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>95</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>50</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
       <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>PG9003</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>QG9003</t>
         </is>
@@ -1996,45 +2064,46 @@
           <t>elite_ice_lord</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>冰霜巨人王</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>120</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>7</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>50</v>
       </c>
-      <c r="J28" t="n">
-        <v>1</v>
-      </c>
       <c r="K28" t="n">
+        <v>1</v>
+      </c>
+      <c r="L28" t="n">
         <v>2</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>PG9004</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>QG9004</t>
         </is>
@@ -2051,45 +2120,46 @@
           <t>elite_infernal</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>地狱火</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>3</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>100</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>12</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>50</v>
       </c>
-      <c r="J29" t="n">
-        <v>1</v>
-      </c>
       <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
         <v>2</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>PG9005</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>QG9005</t>
         </is>
@@ -2106,45 +2176,46 @@
           <t>elite_dark_iron</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>黑铁议员</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>3</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>90</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>9</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>50</v>
       </c>
-      <c r="J30" t="n">
-        <v>1</v>
-      </c>
       <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
         <v>2</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>PG9006</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>QG9006</t>
         </is>
@@ -2161,45 +2232,46 @@
           <t>elite_doomguard</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>末日守卫</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>4</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>110</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>11</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>50</v>
       </c>
-      <c r="J31" t="n">
-        <v>1</v>
-      </c>
       <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>PG9007</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>QG9007</t>
         </is>
@@ -2216,45 +2288,46 @@
           <t>elite_shadow_priest</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>暗影大主教</t>
         </is>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>4</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>PRIEST</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>80</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>8</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>50</v>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
       <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>PG9008</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>QG9008</t>
         </is>
@@ -2271,45 +2344,46 @@
           <t>elite_titan_construct</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>泰坦守护者</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>5</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>130</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>10</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>50</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
       <c r="K33" t="n">
+        <v>1</v>
+      </c>
+      <c r="L33" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>PG9009</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>QG9009</t>
         </is>
@@ -2326,45 +2400,46 @@
           <t>elite_void_walker</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>虚空行者</t>
         </is>
       </c>
-      <c r="D34" t="n">
+      <c r="E34" t="n">
         <v>5</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>ELITE</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>90</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>13</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>50</v>
       </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
       <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
         <v>2</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>PG9010</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>QG9010</t>
         </is>
@@ -2383,43 +2458,48 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>枯骨巫妖</t>
         </is>
       </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>150</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>10</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>60</v>
       </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
       <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="inlineStr">
         <is>
           <t>PG9101</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>QG9101</t>
         </is>
@@ -2438,43 +2518,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>m10001</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>远古树王</t>
         </is>
       </c>
-      <c r="D36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>300</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>15</v>
       </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="inlineStr">
         <is>
           <t>PG9102</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>QG9102</t>
         </is>
@@ -2491,45 +2576,46 @@
           <t>boss_frost_queen</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>霜寒女王</t>
         </is>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>2</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>160</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>10</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>60</v>
       </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
       <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>PG9103</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>QG9103</t>
         </is>
@@ -2546,45 +2632,46 @@
           <t>boss_frost_lich</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>霜之巫妖王</t>
         </is>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>2</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>320</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>15</v>
       </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>PG9104</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>QG9104</t>
         </is>
@@ -2601,45 +2688,46 @@
           <t>boss_ragnaros</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>炎魔之王</t>
         </is>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>3</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>WARRIOR</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>200</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>12</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>60</v>
       </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
       <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="inlineStr">
         <is>
           <t>PG9105</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>QG9105</t>
         </is>
@@ -2656,45 +2744,46 @@
           <t>boss_deathwing</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>熔火死翼</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>3</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>380</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>16</v>
       </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="inlineStr">
         <is>
           <t>PG9106</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>QG9106</t>
         </is>
@@ -2711,45 +2800,46 @@
           <t>boss_archimonde</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>深渊领主</t>
         </is>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>4</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>200</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>11</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>60</v>
       </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
       <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="inlineStr">
         <is>
           <t>PG9107</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>QG9107</t>
         </is>
@@ -2766,45 +2856,46 @@
           <t>boss_kiljaeden</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>暗影之王</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="E42" t="n">
         <v>4</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>380</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>16</v>
       </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
         <is>
           <t>PG9108</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>QG9108</t>
         </is>
@@ -2821,45 +2912,46 @@
           <t>boss_titan_watcher</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
         <is>
           <t>泰坦看守者</t>
         </is>
       </c>
-      <c r="D43" t="n">
+      <c r="E43" t="n">
         <v>5</v>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>GUARDIAN</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>200</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>12</v>
       </c>
-      <c r="I43" t="n">
+      <c r="J43" t="n">
         <v>60</v>
       </c>
-      <c r="J43" t="n">
-        <v>1</v>
-      </c>
       <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
         <is>
           <t>PG9109</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>QG9109</t>
         </is>
@@ -2876,45 +2968,46 @@
           <t>boss_eternal_lord</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
         <is>
           <t>永恒主宰</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="E44" t="n">
         <v>5</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>BOSS</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>CASTER</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>480</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>18</v>
       </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
         <is>
           <t>PG9110</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>QG9110</t>
         </is>
